--- a/AAII_Financials/Quarterly/RSG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RSG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="92">
   <si>
     <t>RSG</t>
   </si>
@@ -656,543 +656,556 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>4430000</v>
+      </c>
+      <c r="E8" s="3">
         <v>4113000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>4135000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>4212000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>4235000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>4009000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>4046000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>4076000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>4048000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3862000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3832100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>3825900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>3725900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3581100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>3529800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>3597800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>3413600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2968800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2952800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2933900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2812800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2596400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2573200</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>2572100</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>2454400</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>2553900</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>2576700</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>2646900</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>2605300</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>2470600</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>2530000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>2565700</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>2517800</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>2427500</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>2560000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>2562000</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>2526700</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>2392800</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>2379200</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>2409300</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>2563000</v>
+      </c>
+      <c r="E9" s="3">
         <v>2366000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>2230000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>2463000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>2449000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>2314000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2136000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2367000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2383000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2283000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2089000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2284300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2224400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2169500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>2184600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>2193000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>2063400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1762300</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1809700</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1744000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1650700</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1534300</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1547200</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1535400</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1468100</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1558100</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1520300</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1606700</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1592500</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>1482500</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>1525600</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>1577400</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>1577200</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>1469800</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>1593000</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>1580100</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>1557400</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>1484100</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>1465300</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>1476700</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1867000</v>
+      </c>
+      <c r="E10" s="3">
         <v>1747000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1905000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1749000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1786000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1695000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1910000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1709000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1665000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1579000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1743100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1541600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1501500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1411600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1345200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1404800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1350200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1206500</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1143100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1189900</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1162100</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1062100</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1026000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1036700</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>986300</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>995800</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1056400</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1040200</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1012800</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>988100</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1004400</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>988300</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>940600</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>957700</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>967000</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>981900</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>969300</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>908700</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>913900</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>932600</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1235,8 +1248,9 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1357,8 +1371,11 @@
       <c r="AP12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1479,252 +1496,261 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E14" s="3">
         <v>1000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>7000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>3000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>9000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>2000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>9000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>11000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>4000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>6000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>12700</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>11000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>26100</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>13300</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>20100</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>15500</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>57800</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>10800</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>5400</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>4600</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>3800</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>2800</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>94900</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>55300</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>35000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>-1100</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>17100</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>8500</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>1500</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>3000</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>15900</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>9200</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>4100</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>9500</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>6200</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>3700</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AN14" s="3">
         <v>4100</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AO14" s="3">
         <v>4400</v>
       </c>
-      <c r="AO14" s="3">
+      <c r="AP14" s="3">
         <v>7200</v>
       </c>
-      <c r="AP14" s="3">
+      <c r="AQ14" s="3">
         <v>203400</v>
       </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>488000</v>
+      </c>
+      <c r="E15" s="3">
         <v>461000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>458000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>459000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>463000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>434000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>443000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>422000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>413000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>399000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>401600</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>382300</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>358300</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>358700</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>349800</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>353900</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>337600</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>310400</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>299000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>301300</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>303000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>282100</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>267500</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>270700</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>269100</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>268600</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>257400</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>267300</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>264200</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>251500</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>252400</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>262400</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>255500</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>263100</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>267300</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>260800</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>258300</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>249900</v>
       </c>
-      <c r="AO15" s="3">
+      <c r="AP15" s="3">
         <v>245400</v>
       </c>
-      <c r="AP15" s="3">
+      <c r="AQ15" s="3">
         <v>252400</v>
       </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1764,252 +1790,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3525000</v>
+      </c>
+      <c r="E17" s="3">
         <v>3282000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>3329000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>3373000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>3365000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>3203000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>3242000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>3213000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3230000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3123000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>3112400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>3087100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2992600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2923900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2952600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2933500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2824000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2408200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2451100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2369700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2294900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2104000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2207900</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2158700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2059200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2120900</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>2117500</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>2179100</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>2167900</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>2047800</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>2046800</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>2125400</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>2109900</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>2023300</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>2154000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>2113900</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>2101200</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>2004700</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>1987300</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>2187600</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>905000</v>
+      </c>
+      <c r="E18" s="3">
         <v>831000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>806000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>839000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>870000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>806000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>804000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>863000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>818000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>739000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>719700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>738800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>733300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>657200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>577200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>664300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>589600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>560600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>501700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>564200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>517900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>492400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>365300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>413400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>395200</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>433000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>459200</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>467800</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>437400</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>422800</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>483200</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>440300</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>407900</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>404200</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>406000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>448100</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>425500</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>388100</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>391900</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>221700</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2052,252 +2085,259 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>53000</v>
+      </c>
+      <c r="E20" s="3">
         <v>25000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>91000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>50000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-2000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>1000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>131000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>71000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>33000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-4000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>96400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-4100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>4200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-3500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-90900</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-51300</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-17500</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-4900</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-145100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-15400</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-12100</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-13900</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-85800</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-5800</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-3500</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-13800</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-79200</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-300</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-10300</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-9600</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-29400</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-4000</v>
-      </c>
-      <c r="AI20" s="3">
-        <v>1200</v>
       </c>
       <c r="AJ20" s="3">
         <v>1200</v>
       </c>
       <c r="AK20" s="3">
+        <v>1200</v>
+      </c>
+      <c r="AL20" s="3">
         <v>-17400</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-1400</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>-2600</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>-2500</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>-60600</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1340000</v>
+      </c>
+      <c r="E21" s="3">
         <v>1267000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1173000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1248000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1335000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1239000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1116000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1214000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1198000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1142000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1024900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1125200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1087400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1019400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>858800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>989700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>932000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>887800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>676400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>912000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>808900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>760600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>567500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>699000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>681600</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>708700</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>657900</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>755300</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>711800</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>685200</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>726200</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>718800</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>684800</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>688900</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>675800</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>727500</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>701100</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>655500</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>596500</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>495300</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2305,365 +2345,374 @@
         <v>151000</v>
       </c>
       <c r="E22" s="3">
+        <v>151000</v>
+      </c>
+      <c r="F22" s="3">
         <v>146000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>143000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>145000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>140000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>133000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>138000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>128000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>139000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>129200</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>127600</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>124400</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>126700</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>112900</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>105200</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>94000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>83500</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>79700</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>78100</v>
-      </c>
-      <c r="W22" s="3">
-        <v>78400</v>
       </c>
       <c r="X22" s="3">
         <v>78400</v>
       </c>
       <c r="Y22" s="3">
+        <v>78400</v>
+      </c>
+      <c r="Z22" s="3">
         <v>78200</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>88900</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>91600</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>96600</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>95100</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>98000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>98500</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>100400</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>96500</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>96000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>96500</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>94800</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>92900</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>90000</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>89500</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>89400</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>36600</v>
       </c>
-      <c r="AP22" s="3">
+      <c r="AQ22" s="3">
         <v>96300</v>
       </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>699000</v>
+      </c>
+      <c r="E23" s="3">
         <v>656000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>564000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>645000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>720000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>665000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>533000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>647000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>654000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>599000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>482400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>606300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>580200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>522100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>373400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>507800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>478100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>472200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>276900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>470700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>427400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>400100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>201300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>318700</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>300100</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>322600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>284900</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>369500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>328600</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>312800</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>357300</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>340300</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>312600</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>310600</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>295700</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>356700</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>333400</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>296200</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>294700</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>126900</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>133000</v>
+      </c>
+      <c r="E24" s="3">
         <v>131000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>20000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>95000</v>
-      </c>
-      <c r="G24" s="3">
-        <v>170000</v>
       </c>
       <c r="H24" s="3">
         <v>170000</v>
       </c>
       <c r="I24" s="3">
+        <v>170000</v>
+      </c>
+      <c r="J24" s="3">
         <v>20000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>81000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>142000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>145000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>43100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>126000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>152600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>138200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>26400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>90900</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>106300</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>120300</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-36200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>119900</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>95400</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>103700</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-35000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>58500</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>73800</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>75800</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-5100</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>71500</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>77700</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>77900</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>55900</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>77400</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>76900</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>72700</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>95100</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>133400</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>130000</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>108400</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>105100</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>41200</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2784,252 +2833,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>566000</v>
+      </c>
+      <c r="E26" s="3">
         <v>525000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>544000</v>
-      </c>
-      <c r="F26" s="3">
-        <v>550000</v>
       </c>
       <c r="G26" s="3">
         <v>550000</v>
       </c>
       <c r="H26" s="3">
+        <v>550000</v>
+      </c>
+      <c r="I26" s="3">
         <v>495000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>513000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>566000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>512000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>454000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>439300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>480300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>427600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>383900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>347000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>416900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>371800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>351900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>313100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>350800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>332000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>296400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>236300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>260200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>226300</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>246800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>290000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>298000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>250900</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>234900</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>301400</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>262900</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>235700</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>237900</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>200600</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>223300</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>203400</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>187800</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>189600</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>85700</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>566000</v>
+      </c>
+      <c r="E27" s="3">
         <v>525000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>544000</v>
-      </c>
-      <c r="F27" s="3">
-        <v>550000</v>
       </c>
       <c r="G27" s="3">
         <v>550000</v>
       </c>
       <c r="H27" s="3">
+        <v>550000</v>
+      </c>
+      <c r="I27" s="3">
         <v>495000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>512000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>566000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>512000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>454000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>439600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>480200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>427400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>383900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>346800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>416900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>371900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>352000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>313100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>350300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>331100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>295900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>235400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>260000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>225500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>246300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>289300</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>298300</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>251500</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>234200</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>301200</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>263400</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>234900</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>237700</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>200500</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>223200</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>202900</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>187800</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>189500</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>85600</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3150,8 +3208,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3224,8 +3285,8 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-      <c r="AA29" s="3" t="s">
-        <v>8</v>
+      <c r="AA29" s="3">
+        <v>0</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>8</v>
@@ -3242,11 +3303,11 @@
       <c r="AF29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AG29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH29" s="3">
         <v>-300</v>
-      </c>
-      <c r="AH29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AI29" s="3" t="s">
         <v>8</v>
@@ -3254,11 +3315,11 @@
       <c r="AJ29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AK29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL29" s="3">
         <v>463900</v>
-      </c>
-      <c r="AL29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AM29" s="3" t="s">
         <v>8</v>
@@ -3272,8 +3333,11 @@
       <c r="AP29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3394,8 +3458,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3516,252 +3583,261 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-53000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-25000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-91000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-50000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>2000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-1000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-131000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-71000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-33000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>4000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-96400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>4100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-4200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>3500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>90900</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>51300</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>17500</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>4900</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>145100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>15400</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>12100</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>13900</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>85800</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>5800</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>3500</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>13800</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>79200</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>300</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>10300</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>9600</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>29400</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>4000</v>
-      </c>
-      <c r="AI32" s="3">
-        <v>-1200</v>
       </c>
       <c r="AJ32" s="3">
         <v>-1200</v>
       </c>
       <c r="AK32" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="AL32" s="3">
         <v>17400</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>1400</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>2600</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>2500</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>60600</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>566000</v>
+      </c>
+      <c r="E33" s="3">
         <v>525000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>544000</v>
-      </c>
-      <c r="F33" s="3">
-        <v>550000</v>
       </c>
       <c r="G33" s="3">
         <v>550000</v>
       </c>
       <c r="H33" s="3">
+        <v>550000</v>
+      </c>
+      <c r="I33" s="3">
         <v>495000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>512000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>566000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>512000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>454000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>439600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>480200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>427400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>383900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>346800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>416900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>371900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>352000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>313100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>350300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>331100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>295900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>235400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>260000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>225500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>246300</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>289300</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>298300</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>251500</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>234200</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>300900</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>263400</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>234900</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>237700</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>664400</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>223200</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>202900</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>187800</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>189500</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>85600</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3882,257 +3958,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>566000</v>
+      </c>
+      <c r="E35" s="3">
         <v>525000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>544000</v>
-      </c>
-      <c r="F35" s="3">
-        <v>550000</v>
       </c>
       <c r="G35" s="3">
         <v>550000</v>
       </c>
       <c r="H35" s="3">
+        <v>550000</v>
+      </c>
+      <c r="I35" s="3">
         <v>495000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>512000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>566000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>512000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>454000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>439600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>480200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>427400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>383900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>346800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>416900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>371900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>352000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>313100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>350300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>331100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>295900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>235400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>260000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>225500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>246300</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>289300</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>298300</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>251500</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>234200</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>300900</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>263400</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>234900</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>237700</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>664400</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>223200</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>202900</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>187800</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>189500</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>85600</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4175,8 +4260,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4219,130 +4305,134 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>107000</v>
+      </c>
+      <c r="E41" s="3">
         <v>118000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>76000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>84000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>122000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>83000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>74000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>83400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>490600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>91600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>140000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>157500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>181600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>132200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>143400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>81400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>119400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>39000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>29000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>40100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>34000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>23200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>38200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>406400</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>269700</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>281600</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>47100</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>55600</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>72500</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>68000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>70500</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>81900</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>61300</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>62600</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>83300</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>63900</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>36000</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>33200</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>67800</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>55000</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4415,14 +4505,14 @@
       <c r="Z42" s="3">
         <v>0</v>
       </c>
-      <c r="AA42" s="3" t="s">
+      <c r="AA42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>25000</v>
-      </c>
-      <c r="AC42" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AD42" s="3" t="s">
         <v>8</v>
@@ -4445,11 +4535,11 @@
       <c r="AJ42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AK42" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL42" s="3">
         <v>3000</v>
-      </c>
-      <c r="AL42" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AM42" s="3" t="s">
         <v>8</v>
@@ -4463,862 +4553,886 @@
       <c r="AP42" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ42" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2199000</v>
+      </c>
+      <c r="E43" s="3">
         <v>2114000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2169000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2090000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2051000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1977000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2071000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1976800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1942600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1919300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1992000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1927800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1876700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1875400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1982900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1853000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1805000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1473200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1508400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1342400</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1299600</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1259200</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1328300</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1199200</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>1161200</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>1295500</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>1402600</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>1250900</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>1265600</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>1234600</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>1350500</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>1246500</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>1176300</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>1147700</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>1217300</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>1193900</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>1137300</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>1077100</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>1092700</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>1109800</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>115000</v>
+      </c>
+      <c r="E44" s="3">
         <v>114000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>106000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>103000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>104000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>102000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>98000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>97700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>99900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>101400</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>98000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>100000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>96100</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>97900</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>96600</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>101100</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>100200</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>80500</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>72200</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>68200</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>63900</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>61100</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>59100</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>58800</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>58500</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>57100</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>56800</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>55300</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>56200</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>55400</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>53100</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>55400</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>52800</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>52300</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>51200</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>47800</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>45400</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>45000</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>44000</v>
       </c>
-      <c r="AP44" s="3">
+      <c r="AQ44" s="3">
         <v>43700</v>
       </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>54000</v>
+      </c>
+      <c r="E45" s="3">
         <v>56000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>41000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>37000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>40000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>42000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>36000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>37100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>32300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>37000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>28000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>28100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>20600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>25100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>134200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>163900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>116000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>103100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>101200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>118700</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>83400</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>99600</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>96200</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>109900</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>79400</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>94700</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>99500</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>112100</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>79800</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>86600</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>90300</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>108300</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>79000</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>91400</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>82000</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>91100</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>74100</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>79100</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>80000</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>93100</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2563000</v>
+      </c>
+      <c r="E46" s="3">
         <v>2510000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2523000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2484000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2416000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2321000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2406000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2348400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2659700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2273600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2381000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2348400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2261700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2241400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>2357100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>2199400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>2140600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1695800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1710800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>1569400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>1480900</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>1443100</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>1521800</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>1774300</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>1568800</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>1753900</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>1606000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>1473900</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>1474100</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>1444600</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>1564400</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>1492100</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>1369400</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>1354000</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>1436800</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>1396700</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>1292800</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>1234400</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>1284500</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>1301600</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>715000</v>
+      </c>
+      <c r="E47" s="3">
         <v>769000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>815000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>824000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>703000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>638000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>637000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>713900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>645300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>672100</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>469000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>481900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>440200</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>441000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>386000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>379600</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>341200</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>233000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>226500</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>232000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>242400</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>234700</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>248700</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>239700</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>196600</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>215000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>198500</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>169400</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>173100</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>170400</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>171500</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>139300</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>131600</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>125400</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>121800</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>116400</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>118400</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>118800</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>122200</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>89200</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>13125000</v>
+      </c>
+      <c r="E48" s="3">
         <v>12902000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>12847000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>12412000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>12285000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>12184000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>12109000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>11756200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>11677700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>11539400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>11589000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>10939400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>10800500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>10922000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>11019100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>10718800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>10695300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>9439200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>9487400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>9182900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>9036300</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>8900000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>8945000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>8759500</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>8730400</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>8680000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>8627100</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>8500700</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>8326700</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>8217700</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>8020100</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>7913900</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>7863500</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>7783100</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>7777400</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>7750100</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>7690100</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>7592800</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>7588600</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>7616000</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>17893000</v>
+      </c>
+      <c r="E49" s="3">
         <v>17573000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>17370000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>17298000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>17238000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>17217000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>16528000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>16337900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>16328300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>16334900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>16330000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>15737900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>15785100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>14977700</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>14798700</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>14593600</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>14565000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>13090700</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>13085500</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>12964400</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>12685600</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>12228700</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>12219500</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>11839600</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>11800200</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>11797500</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>11767300</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>11774600</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>11623500</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>11546700</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>11506600</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>11488100</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>11460700</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>11450400</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>11456500</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>11385700</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>11365700</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>11357300</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>11345500</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>11364500</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5439,8 +5553,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5561,130 +5678,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>613000</v>
+      </c>
+      <c r="E52" s="3">
         <v>604000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>571000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>541000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>529000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>525000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>517000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>453300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>432300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>396400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>490000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>390200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>395200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>361000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>492000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>509600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>470800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>421400</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>444800</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>480200</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>476900</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>446100</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>499000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>497000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>530300</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>462500</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>484900</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>410500</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>399400</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>402600</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>354400</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>368700</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>378500</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>395800</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>354500</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>299700</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>294100</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>292500</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>288800</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>290400</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5805,130 +5928,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>35159000</v>
+      </c>
+      <c r="E54" s="3">
         <v>34600000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>34366000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>33789000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>33397000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>33103000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>32402000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>31814200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>31934100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>31381700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>31410000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>30042800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>29823300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>29081400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>29052900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>28401000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>28212900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>24880100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>24955000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>24428900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>23922100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>23252600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>23434000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>23110100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>22826300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>22908900</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>22683800</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>22329100</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>21996800</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>21782000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>21617000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>21402100</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>21203700</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>21108700</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>21147000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>20948600</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>20761100</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>20595800</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>20629600</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>20661700</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5971,8 +6100,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -6015,740 +6145,759 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1440000</v>
+      </c>
+      <c r="E57" s="3">
         <v>1196000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1374000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1247000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1199000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1154000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1345000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1225400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1285500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1179200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1412000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1198200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1098400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>984200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1221800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1024300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1044600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>846600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>910000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>815000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>728100</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>678300</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>779000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>646300</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>657400</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>660600</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>777900</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>697200</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>719600</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>629600</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>761500</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>661300</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>629800</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>572400</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>598100</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>599300</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>596500</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>520800</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>553800</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>542800</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>597000</v>
+      </c>
+      <c r="E58" s="3">
         <v>596000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>644000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>975000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>476000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>477000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>917000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>567000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1486100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1484900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>987000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>984800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>203700</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>517300</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>456000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>455800</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>313800</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>8800</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>8200</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>8000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>135200</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>168700</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>168100</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>184300</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>60000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>24500</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>929900</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>912800</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>1561300</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>1595600</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>690700</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>690800</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>41900</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>707000</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>706700</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>705700</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>705400</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>6200</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>5800</v>
       </c>
-      <c r="AP58" s="3">
+      <c r="AQ58" s="3">
         <v>5700</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>689000</v>
+      </c>
+      <c r="E59" s="3">
         <v>686000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>714000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>728000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>696000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>705000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>680000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>690400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>684300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>647900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>652000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>765600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>624000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>623600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1712900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1683700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1576200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1402700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1497400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1510400</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1451500</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1301800</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1334900</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1360200</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>1348700</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>1295500</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>1356800</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>1387400</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>1290100</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>1242700</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>1266400</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>1323200</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>1317800</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>1280800</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>1330000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>1286500</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>1241100</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>1250200</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>1252400</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>1269400</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>3980000</v>
+      </c>
+      <c r="E60" s="3">
         <v>3740000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>3928000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>4263000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>3647000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>3491000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>4128000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>3641500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>4533600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>4325900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>4228000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>4068800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2987900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>3029300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>3390700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>3163800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>2934600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>2258100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>2415600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>2333400</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>2314800</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>2148800</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>2282000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>2190800</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>2066100</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>1980600</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>3064600</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>2997400</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>3571000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>3467900</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>2718600</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>2675300</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>1989500</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>2560200</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>2634800</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>2591500</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>2543000</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>1777200</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>1812000</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>1817900</v>
       </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>13698000</v>
+      </c>
+      <c r="E61" s="3">
         <v>13491000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>13162000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>12531000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>12740000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>13053000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>12040000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>12294300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>11715400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>11585900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>12082000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>11285400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>12255500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>11779200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>11329500</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>11180400</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>11589500</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>9608900</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>9546200</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>9257000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>8833900</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>8594200</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>8766100</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>8594500</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>8598000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>8952200</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>7758600</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>7705800</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>6883900</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>6801500</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>7646800</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>7556700</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>8215800</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>7499700</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>7480700</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>7152000</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>7075700</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>7663900</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>7653100</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>7739600</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>3485000</v>
+      </c>
+      <c r="E62" s="3">
         <v>3452000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>3423000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>3385000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>3354000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>3282000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>3233000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>3057200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>3109600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>3071700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>3030000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2881300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>2858400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>2799100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>4645900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>4566300</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>4472800</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>4028400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>4013500</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>3959600</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>3990000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>3871300</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>3897100</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>3950700</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>3931300</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>3855900</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>3739700</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>3647400</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>3586700</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>3590000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>3322100</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>3246300</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>3149600</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>3134500</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>3070400</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>3530900</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>3477300</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>3469000</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>3470800</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>3462700</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6869,8 +7018,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6991,8 +7143,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7113,130 +7268,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>23126000</v>
+      </c>
+      <c r="E66" s="3">
         <v>22619000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>22397000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>21917000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>21345000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>21438000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>20995000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>20584000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>20927800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>20561100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>20867000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>19710400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>19618600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>19164100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>19366900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>18911100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>18997500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>15896100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>15976100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>15555600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>15143800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>14619700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>14950100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>14740000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>14599200</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>14791700</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>14565600</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>14352600</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>14043900</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>13862500</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>13689900</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>13480500</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>13357600</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>13196900</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>13188200</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>13276600</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>13098200</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>12912500</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>12938300</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>13022500</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7279,8 +7440,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7401,8 +7563,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7523,8 +7688,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7645,8 +7813,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7767,130 +7938,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>11867000</v>
+      </c>
+      <c r="E72" s="3">
         <v>11493000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>11161000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>10810000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>10455000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>10087000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>9774000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>9443900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>9060700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>8717900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>8434000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>8163500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>7852700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>7582700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>7356300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>7166800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>6907100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>6681400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>6475600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>6309400</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>6106000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>5911200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>5751800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>5652800</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>5529200</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>5433600</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>5317300</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>5155900</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>4987900</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>4857500</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>4750500</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>4571600</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>4430900</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>4309300</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>4152500</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>3603400</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>3496700</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>3402500</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>3324000</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>3243900</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -8011,8 +8188,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8133,8 +8313,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8255,130 +8438,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>12032000</v>
+      </c>
+      <c r="E76" s="3">
         <v>11980000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>11968000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>11871000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>12050000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>11663000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>11405000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>11228800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>11005100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>10819800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>10542000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>10331300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>10203700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>9916500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>9686000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>9489900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>9215400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>8984000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>8978900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>8873300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>8778300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>8632900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>8483900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>8370100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>8227100</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>8117200</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>8118200</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>7976500</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>7952900</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>7919500</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>7927100</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>7921600</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>7846100</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>7911800</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>7958800</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>7672000</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>7662900</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>7683300</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>7691300</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>7639200</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8499,257 +8688,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>566000</v>
+      </c>
+      <c r="E81" s="3">
         <v>525000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>544000</v>
-      </c>
-      <c r="F81" s="3">
-        <v>550000</v>
       </c>
       <c r="G81" s="3">
         <v>550000</v>
       </c>
       <c r="H81" s="3">
+        <v>550000</v>
+      </c>
+      <c r="I81" s="3">
         <v>495000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>512000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>566000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>512000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>454000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>439600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>480200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>427400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>383900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>346800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>416900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>371900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>352000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>313100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>350300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>331100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>295900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>235400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>260000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>225500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>246300</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>289300</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>298300</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>251500</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>234200</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>300900</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>263400</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>234900</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>237700</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>664400</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>223200</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>202900</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>187800</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>189500</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>85600</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8792,130 +8990,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>441000</v>
+      </c>
+      <c r="E83" s="3">
         <v>413000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>337000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>404000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>395000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>381000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>316000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>365100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>343300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>343600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>282400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>339000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>323800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>300400</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>372500</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>376700</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>359900</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>332100</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>319800</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>363200</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>303100</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>282100</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>288000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>291400</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>289900</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>289500</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>277900</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>287800</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>284700</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>272000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>272400</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>282500</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>275700</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>283500</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>287200</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>280800</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>278200</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>269900</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>265200</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>272100</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9036,8 +9238,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9158,8 +9363,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9280,8 +9488,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9402,8 +9613,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9524,130 +9738,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1153000</v>
+      </c>
+      <c r="E89" s="3">
         <v>1227000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>981000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1181000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1109000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1025000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1022000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1003000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1100000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>811000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>898700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>953100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1078500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>687700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>806600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>819900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>857900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>705600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>648900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>655000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>821800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>661000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>562600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>575500</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>737700</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>595800</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>565200</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>651300</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>581900</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>553700</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>495900</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>555900</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>609600</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>581400</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>528600</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>502900</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>434900</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>444300</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>488200</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>515300</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9690,130 +9910,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-392000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-476000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-577000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-444000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-407000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-459000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-498000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-439000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-403000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-515000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-547800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-368900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-335700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-378600</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-529200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-277500</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-313200</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-334100</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-412100</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-295600</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-277600</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-331000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-305600</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-234300</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-307900</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-346800</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-298800</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-319600</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-289400</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-299300</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-251300</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-278400</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-278800</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-263300</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-220800</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-271500</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-273600</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-223900</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-189100</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-226700</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9934,8 +10158,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10056,130 +10283,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-817000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-910000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-742000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-756000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-527000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1288000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-812000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-636000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-434000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-679000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1566200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-426500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1021000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-653300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-722100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-417000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-2884500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-399400</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-680500</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-652500</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-788500</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-344600</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-889900</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-311100</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-286400</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-435400</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-402400</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-554000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-403500</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-359100</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-297400</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-325700</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-329300</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-276700</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-418600</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-321100</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-298300</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-292200</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-208800</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-235200</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10222,130 +10455,134 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>192000</v>
+      </c>
+      <c r="E96" s="3">
         <v>193000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>194000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>182000</v>
-      </c>
-      <c r="G96" s="3">
-        <v>181000</v>
       </c>
       <c r="H96" s="3">
         <v>181000</v>
       </c>
       <c r="I96" s="3">
+        <v>181000</v>
+      </c>
+      <c r="J96" s="3">
         <v>182000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>168000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>169000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>168000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>168500</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>156500</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>156600</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>156400</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-156400</v>
-      </c>
-      <c r="R96" s="3">
-        <v>-145300</v>
       </c>
       <c r="S96" s="3">
         <v>-145300</v>
       </c>
       <c r="T96" s="3">
+        <v>-145300</v>
+      </c>
+      <c r="U96" s="3">
         <v>-145900</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-146100</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-135400</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-135600</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-135500</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-135400</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-129200</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-128700</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-129200</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-129300</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-120200</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-120700</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-121000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-121800</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-112300</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-113300</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-114400</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-115700</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-107800</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
         <v>-108400</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>-108600</v>
       </c>
-      <c r="AO96" s="3">
+      <c r="AP96" s="3">
         <v>-109000</v>
       </c>
-      <c r="AP96" s="3">
+      <c r="AQ96" s="3">
         <v>-102800</v>
       </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10466,8 +10703,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10588,8 +10828,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10710,180 +10953,186 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-357000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-238000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-215000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-463000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-544000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>284000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-210000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-753000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-234000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-201000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>641200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-545500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>8300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-42000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-18600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-435900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>2113400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-314700</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>14300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>8400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-9600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-342300</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-47700</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-125900</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-470300</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>31900</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-114000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-112400</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-171200</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-191400</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-202100</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-226000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-281800</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-349600</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-44300</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-150600</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-130200</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-186700</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-266600</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>-267100</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3" t="s">
+      <c r="D101" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-3000</v>
       </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
       <c r="G101" s="3">
+        <v>0</v>
+      </c>
+      <c r="H101" s="3">
         <v>2000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-1000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>800</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>500</v>
       </c>
-      <c r="L101" s="3" t="s">
+      <c r="M101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>600</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-3000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-100</v>
       </c>
-      <c r="P101" s="3" t="s">
+      <c r="Q101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>600</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-3000</v>
-      </c>
-      <c r="S101" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="T101" s="3" t="s">
         <v>8</v>
@@ -10900,8 +11149,8 @@
       <c r="X101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y101" s="3">
-        <v>0</v>
+      <c r="Y101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Z101" s="3">
         <v>0</v>
@@ -10954,126 +11203,132 @@
       <c r="AP101" s="3">
         <v>0</v>
       </c>
+      <c r="AQ101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-21000</v>
+      </c>
+      <c r="E102" s="3">
         <v>78000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>24000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-38000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>39000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>21000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-3000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-386000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>434000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-70000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-25500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-19200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>66300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-7600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>66500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-36000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>86700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-8500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-17300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>10900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>23700</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-25900</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-375000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>138500</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>7300</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>166000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>48800</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-15100</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>7200</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>3200</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-3600</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>4200</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-1500</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-44900</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>64000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>30900</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>5800</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-34600</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>12800</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>13000</v>
       </c>
     </row>
